--- a/artfynd/S 479-2025 artfynd.xlsx
+++ b/artfynd/S 479-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108419172</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122095239</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122095141</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122095139</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1191,6 +1216,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108419137</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108259679</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1400,6 +1435,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108419228</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1511,6 +1551,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108419225</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1627,6 +1672,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108347101</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1744,6 +1794,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108350374</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1864,6 +1919,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108350560</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1970,8 +2030,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108419588</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>